--- a/Operations/Waypoint-GTM-IT-Project-Plan-v1.xlsx
+++ b/Operations/Waypoint-GTM-IT-Project-Plan-v1.xlsx
@@ -743,7 +743,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26.85" customHeight="1" s="27">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -1617,7 +1616,7 @@
       </c>
       <c r="G24" s="39" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="H24" s="36" t="inlineStr">
@@ -1627,7 +1626,7 @@
       </c>
       <c r="I24" s="36" t="inlineStr">
         <is>
-          <t>User can save any action step</t>
+          <t>Save as Action button on AI response bubbles (Mar 15)</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1946,7 @@
       </c>
       <c r="G32" s="39" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="H32" s="34" t="inlineStr">
@@ -1957,7 +1956,7 @@
       </c>
       <c r="I32" s="34" t="inlineStr">
         <is>
-          <t>Local push notifications</t>
+          <t>useNotifications.ts hook with deadline scheduling (Mar 15)</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2276,7 @@
       </c>
       <c r="G40" s="40" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="H40" s="36" t="inlineStr">
@@ -2287,7 +2286,7 @@
       </c>
       <c r="I40" s="36" t="inlineStr">
         <is>
-          <t>Expo notifications, 7-day and 1-day alerts</t>
+          <t>useNotifications.ts — 30/14/7/1-day + same-day reminders (Mar 15)</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2981,7 @@
       </c>
       <c r="G57" s="42" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H57" s="43" t="inlineStr">
@@ -2992,7 +2991,7 @@
       </c>
       <c r="I57" s="34" t="inlineStr">
         <is>
-          <t>WCAG 2.1 AA compliance</t>
+          <t>accessibility.ts utilities + labels on Home/Profile/Navigator. Device audit pending.</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3446,7 @@
       </c>
       <c r="G68" s="42" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="H68" s="34" t="inlineStr">
@@ -3457,7 +3456,7 @@
       </c>
       <c r="I68" s="34" t="inlineStr">
         <is>
-          <t>Error tracking + performance monitoring</t>
+          <t>sentry.ts with PII scrubbing, App.tsx integrated (Mar 15)</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3685,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75" ht="15" customHeight="1" s="27">
       <c r="A75" s="45" t="inlineStr">
         <is>
@@ -4396,7 +4394,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="27">
       <c r="A3" s="30" t="inlineStr">
         <is>

--- a/Operations/Waypoint-GTM-IT-Project-Plan-v1.xlsx
+++ b/Operations/Waypoint-GTM-IT-Project-Plan-v1.xlsx
@@ -1614,7 +1614,7 @@
           <t>S2 / W2</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="35" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1944,7 +1944,7 @@
           <t>S3 / W4</t>
         </is>
       </c>
-      <c r="G32" s="39" t="inlineStr">
+      <c r="G32" s="35" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2274,7 +2274,7 @@
           <t>S4 / W6</t>
         </is>
       </c>
-      <c r="G40" s="40" t="inlineStr">
+      <c r="G40" s="35" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2979,7 +2979,7 @@
           <t>S6 / W10</t>
         </is>
       </c>
-      <c r="G57" s="42" t="inlineStr">
+      <c r="G57" s="39" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -3444,7 +3444,7 @@
           <t>S7 / W11</t>
         </is>
       </c>
-      <c r="G68" s="42" t="inlineStr">
+      <c r="G68" s="35" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
